--- a/sql/mysql/fqc/fqc_数据库表头0707.xlsx
+++ b/sql/mysql/fqc/fqc_数据库表头0707.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="155">
   <si>
     <t>字段名</t>
   </si>
@@ -325,16 +325,37 @@
     <t>员工姓名</t>
   </si>
   <si>
-    <t>state</t>
+    <t>record_date</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>考勤日期</t>
+  </si>
+  <si>
+    <t>后端</t>
+  </si>
+  <si>
+    <t>am_state</t>
   </si>
   <si>
     <t>1-在岗 2-FAT 3-耐压 4-请假 5-离职</t>
   </si>
   <si>
+    <t>pm_state</t>
+  </si>
+  <si>
     <t>task_type</t>
   </si>
   <si>
     <t>任务类型 1-耐压 2-功能</t>
+  </si>
+  <si>
+    <t>task_date</t>
+  </si>
+  <si>
+    <t>任务日期</t>
   </si>
   <si>
     <t>sn_code1</t>
@@ -2675,8 +2696,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="15.9083333333333" customWidth="1"/>
     <col min="4" max="4" width="16.5416666666667" customWidth="1"/>
@@ -2835,7 +2856,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
@@ -2843,17 +2864,17 @@
       <c r="D6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="2">
-        <v>1</v>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>15</v>
@@ -2861,28 +2882,28 @@
     </row>
     <row r="7" ht="18.75" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>15</v>
@@ -2890,30 +2911,117 @@
     </row>
     <row r="8" ht="18.75" spans="1:9">
       <c r="A8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" spans="1:9">
+      <c r="A10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2926,7 +3034,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.0916666666667" customWidth="1"/>
@@ -3084,7 +3192,7 @@
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>38</v>
@@ -3093,13 +3201,13 @@
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
@@ -3113,36 +3221,34 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>22</v>
+        <v>107</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
@@ -3157,15 +3263,21 @@
         <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+        <v>109</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -3180,16 +3292,15 @@
         <v>28</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
-      <c r="J9" s="2"/>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
@@ -3204,15 +3315,16 @@
         <v>28</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
@@ -3227,7 +3339,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -3235,7 +3347,7 @@
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
@@ -3250,7 +3362,7 @@
         <v>28</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -3258,7 +3370,7 @@
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>17</v>
@@ -3273,7 +3385,7 @@
         <v>28</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -3281,7 +3393,7 @@
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>17</v>
@@ -3296,7 +3408,7 @@
         <v>28</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -3304,7 +3416,7 @@
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>17</v>
@@ -3319,7 +3431,7 @@
         <v>28</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -3327,7 +3439,7 @@
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>17</v>
@@ -3342,30 +3454,30 @@
         <v>28</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:9">
-      <c r="A17" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>102</v>
+      <c r="C17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -3373,7 +3485,7 @@
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:9">
       <c r="A18" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>17</v>
@@ -3388,7 +3500,7 @@
         <v>28</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -3396,7 +3508,7 @@
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:9">
       <c r="A19" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>17</v>
@@ -3411,7 +3523,7 @@
         <v>28</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -3419,7 +3531,7 @@
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:9">
       <c r="A20" s="5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>17</v>
@@ -3434,7 +3546,7 @@
         <v>28</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -3442,7 +3554,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:9">
       <c r="A21" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>17</v>
@@ -3457,7 +3569,7 @@
         <v>28</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -3465,7 +3577,7 @@
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:9">
       <c r="A22" s="5" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>17</v>
@@ -3480,7 +3592,7 @@
         <v>28</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -3488,7 +3600,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:9">
       <c r="A23" s="5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>17</v>
@@ -3503,7 +3615,7 @@
         <v>28</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -3511,7 +3623,7 @@
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:9">
       <c r="A24" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>17</v>
@@ -3526,7 +3638,7 @@
         <v>28</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -3534,7 +3646,7 @@
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>17</v>
@@ -3549,7 +3661,7 @@
         <v>28</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -3557,7 +3669,7 @@
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>17</v>
@@ -3572,44 +3684,38 @@
         <v>28</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:9">
-      <c r="A27" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="A27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:9">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>31</v>
@@ -3624,13 +3730,13 @@
         <v>46</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>15</v>
@@ -3638,10 +3744,10 @@
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
@@ -3649,27 +3755,56 @@
       <c r="D29" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1" spans="1:9">
+      <c r="A30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="2">
         <v>0</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="7" t="s">
+      <c r="G30" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="G7:G26"/>
-    <mergeCell ref="H7:H26"/>
-    <mergeCell ref="I7:I26"/>
+    <mergeCell ref="G8:G27"/>
+    <mergeCell ref="H8:H27"/>
+    <mergeCell ref="I8:I27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3737,7 +3872,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -3766,7 +3901,7 @@
         <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>21</v>
@@ -3781,7 +3916,7 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>38</v>
@@ -3796,7 +3931,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>22</v>
@@ -3810,10 +3945,10 @@
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>27</v>
@@ -3825,7 +3960,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>22</v>
@@ -3839,10 +3974,10 @@
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>27</v>
@@ -3854,7 +3989,7 @@
         <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>22</v>
@@ -3868,7 +4003,7 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -3883,7 +4018,7 @@
         <v>28</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>22</v>
@@ -3897,7 +4032,7 @@
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>41</v>
@@ -3912,7 +4047,7 @@
         <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>22</v>
@@ -3941,7 +4076,7 @@
         <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>22</v>
@@ -4019,7 +4154,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
@@ -4033,7 +4168,7 @@
     </row>
     <row r="3" ht="18.75" spans="1:10">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>10</v>
@@ -4048,7 +4183,7 @@
         <v>28</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>21</v>
@@ -4063,7 +4198,7 @@
     </row>
     <row r="4" ht="18.75" spans="1:10">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -4078,7 +4213,7 @@
         <v>28</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>21</v>
@@ -4093,7 +4228,7 @@
     </row>
     <row r="5" ht="18.75" spans="1:10">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
@@ -4108,7 +4243,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
@@ -4123,7 +4258,7 @@
     </row>
     <row r="6" ht="18.75" spans="1:10">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>10</v>
@@ -4138,7 +4273,7 @@
         <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
@@ -4153,7 +4288,7 @@
     </row>
     <row r="7" ht="18.75" spans="1:10">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -4168,7 +4303,7 @@
         <v>28</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
@@ -4243,12 +4378,12 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:10">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" ht="33" customHeight="1" spans="1:10">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
